--- a/data/ams_weekly_data/Nexlev/ads_report_week20.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week20.xlsx
@@ -9219,7 +9219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9384,7 +9384,7 @@
         <v>3928</v>
       </c>
       <c r="E5" t="n">
-        <v>5.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>163.83</v>
@@ -9417,7 +9417,7 @@
         <v>3928</v>
       </c>
       <c r="E6" t="n">
-        <v>5.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
         <v>163.83</v>
@@ -9450,7 +9450,7 @@
         <v>3928</v>
       </c>
       <c r="E7" t="n">
-        <v>5.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>163.83</v>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>421.5</v>
+        <v>422</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>421.5</v>
+        <v>422</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8430.333333333334</v>
+        <v>8430</v>
       </c>
       <c r="E14" t="n">
         <v>14</v>
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8430.333333333334</v>
+        <v>8430</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8430.333333333334</v>
+        <v>8430</v>
       </c>
       <c r="E16" t="n">
         <v>14</v>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -9806,23 +9806,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19659.33333333333</v>
+        <v>22276</v>
       </c>
       <c r="E18" t="n">
-        <v>69.66666666666667</v>
+        <v>79</v>
       </c>
       <c r="F18" t="n">
-        <v>783.6633333333333</v>
+        <v>887.9574831752088</v>
       </c>
       <c r="G18" t="n">
-        <v>3130.796666666667</v>
+        <v>3547.46</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -9839,23 +9839,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19659.33333333333</v>
+        <v>36702</v>
       </c>
       <c r="E19" t="n">
-        <v>69.66666666666667</v>
+        <v>130</v>
       </c>
       <c r="F19" t="n">
-        <v>783.6633333333333</v>
+        <v>1463.032516824791</v>
       </c>
       <c r="G19" t="n">
-        <v>3130.796666666667</v>
+        <v>5844.93</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -9867,28 +9867,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nex_HnK_SB_KT_VC-01/VC-02/VC-05_BCG_Phrase &amp; Exact</t>
+          <t>Nex_Hnk_SBV_KT_ST-01_B0DVC7VJP1_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19659.33333333333</v>
+        <v>549</v>
       </c>
       <c r="E20" t="n">
-        <v>69.66666666666667</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>783.6633333333333</v>
+        <v>234.11</v>
       </c>
       <c r="G20" t="n">
-        <v>3130.796666666667</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -9900,28 +9900,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SBV_KT_ST-01_B0DVC7VJP1_Phrase &amp; Exact</t>
+          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>549</v>
+        <v>25262</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>224</v>
       </c>
       <c r="F21" t="n">
-        <v>234.11</v>
+        <v>8501.830922148376</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>15949.01419905257</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -9938,23 +9938,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11570.33333333333</v>
+        <v>188</v>
       </c>
       <c r="E22" t="n">
-        <v>109.6666666666667</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>4027.913333333333</v>
+        <v>308.5366666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>7687.286666666667</v>
+        <v>818.9266666666667</v>
       </c>
       <c r="H22" t="n">
-        <v>2.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -9971,23 +9971,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11570.33333333333</v>
+        <v>9261</v>
       </c>
       <c r="E23" t="n">
-        <v>109.6666666666667</v>
+        <v>90</v>
       </c>
       <c r="F23" t="n">
-        <v>4027.913333333333</v>
+        <v>3273.372411184956</v>
       </c>
       <c r="G23" t="n">
-        <v>7687.286666666667</v>
+        <v>6293.919134280768</v>
       </c>
       <c r="H23" t="n">
-        <v>2.666666666666667</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -9999,28 +9999,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev - Steam Cleaner - SB - KT - Phrase/Exact</t>
+          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11570.33333333333</v>
+        <v>10002</v>
       </c>
       <c r="E24" t="n">
-        <v>109.6666666666667</v>
+        <v>398</v>
       </c>
       <c r="F24" t="n">
-        <v>4027.913333333333</v>
+        <v>4927.734352504465</v>
       </c>
       <c r="G24" t="n">
-        <v>7687.286666666667</v>
+        <v>26657.11</v>
       </c>
       <c r="H24" t="n">
-        <v>2.666666666666667</v>
+        <v>9</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -10037,23 +10037,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8021.5</v>
+        <v>6041</v>
       </c>
       <c r="E25" t="n">
-        <v>319</v>
+        <v>240</v>
       </c>
       <c r="F25" t="n">
-        <v>3951.805</v>
+        <v>2975.875647495534</v>
       </c>
       <c r="G25" t="n">
-        <v>21377.715</v>
+        <v>16098.32</v>
       </c>
       <c r="H25" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -10065,28 +10065,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev -B0DM6BB3VT-Calf Massager-SBV -KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8021.5</v>
+        <v>31592</v>
       </c>
       <c r="E26" t="n">
-        <v>319</v>
+        <v>145</v>
       </c>
       <c r="F26" t="n">
-        <v>3951.805</v>
+        <v>2361.43</v>
       </c>
       <c r="G26" t="n">
-        <v>21377.715</v>
+        <v>8050.47</v>
       </c>
       <c r="H26" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -10098,28 +10098,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15796</v>
+        <v>23496</v>
       </c>
       <c r="E27" t="n">
-        <v>72.5</v>
+        <v>132</v>
       </c>
       <c r="F27" t="n">
-        <v>1180.715</v>
+        <v>2497.05005429707</v>
       </c>
       <c r="G27" t="n">
-        <v>4025.235</v>
+        <v>8598.58829355168</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -10131,28 +10131,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15796</v>
+        <v>7122</v>
       </c>
       <c r="E28" t="n">
-        <v>72.5</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
-        <v>1180.715</v>
+        <v>756.8499457029299</v>
       </c>
       <c r="G28" t="n">
-        <v>4025.235</v>
+        <v>2606.21170644832</v>
       </c>
       <c r="H28" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -10164,28 +10164,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10206</v>
+        <v>10846</v>
       </c>
       <c r="E29" t="n">
-        <v>57.33333333333334</v>
+        <v>381</v>
       </c>
       <c r="F29" t="n">
-        <v>1084.633333333333</v>
+        <v>4433.143570811519</v>
       </c>
       <c r="G29" t="n">
-        <v>3734.933333333333</v>
+        <v>4201.436002353909</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -10197,28 +10197,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10206</v>
+        <v>3053</v>
       </c>
       <c r="E30" t="n">
-        <v>57.33333333333334</v>
+        <v>107</v>
       </c>
       <c r="F30" t="n">
-        <v>1084.633333333333</v>
+        <v>1247.676429188481</v>
       </c>
       <c r="G30" t="n">
-        <v>3734.933333333333</v>
+        <v>1182.46399764609</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -10230,28 +10230,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10206</v>
+        <v>16439</v>
       </c>
       <c r="E31" t="n">
-        <v>57.33333333333334</v>
+        <v>443</v>
       </c>
       <c r="F31" t="n">
-        <v>1084.633333333333</v>
+        <v>7053.09</v>
       </c>
       <c r="G31" t="n">
-        <v>3734.933333333333</v>
+        <v>29738.12</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -10263,28 +10263,28 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6949.5</v>
+        <v>2485</v>
       </c>
       <c r="E32" t="n">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>2840.41</v>
+        <v>534.1999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>2691.95</v>
+        <v>5949.5</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -10296,28 +10296,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6949.5</v>
+        <v>2215</v>
       </c>
       <c r="E33" t="n">
-        <v>244</v>
+        <v>61</v>
       </c>
       <c r="F33" t="n">
-        <v>2840.41</v>
+        <v>1359.899455669874</v>
       </c>
       <c r="G33" t="n">
-        <v>2691.95</v>
+        <v>3895.966416957186</v>
       </c>
       <c r="H33" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -10329,28 +10329,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16439</v>
+        <v>9045</v>
       </c>
       <c r="E34" t="n">
-        <v>443</v>
+        <v>248</v>
       </c>
       <c r="F34" t="n">
-        <v>7053.09</v>
+        <v>5553.29398262411</v>
       </c>
       <c r="G34" t="n">
-        <v>29738.12</v>
+        <v>15909.59299938578</v>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -10362,28 +10362,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1242.5</v>
+        <v>4893</v>
       </c>
       <c r="E35" t="n">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="F35" t="n">
-        <v>267.1</v>
+        <v>3004.056561706017</v>
       </c>
       <c r="G35" t="n">
-        <v>2974.75</v>
+        <v>8606.300583657032</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -10395,28 +10395,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1242.5</v>
+        <v>8041</v>
       </c>
       <c r="E36" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F36" t="n">
-        <v>267.1</v>
+        <v>1061.820125740322</v>
       </c>
       <c r="G36" t="n">
-        <v>2974.75</v>
+        <v>4500.301235885336</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10437,19 +10437,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16153</v>
+        <v>22913</v>
       </c>
       <c r="E37" t="n">
-        <v>442</v>
+        <v>148</v>
       </c>
       <c r="F37" t="n">
-        <v>9917.25</v>
+        <v>3025.882502331749</v>
       </c>
       <c r="G37" t="n">
-        <v>28411.86</v>
+        <v>12824.56645412807</v>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -10466,23 +10466,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12261</v>
+        <v>5829</v>
       </c>
       <c r="E38" t="n">
-        <v>79.33333333333333</v>
+        <v>38</v>
       </c>
       <c r="F38" t="n">
-        <v>1619.15</v>
+        <v>769.7473719279279</v>
       </c>
       <c r="G38" t="n">
-        <v>6862.426666666666</v>
+        <v>3262.412309986596</v>
       </c>
       <c r="H38" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -10494,28 +10494,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12261</v>
+        <v>42343</v>
       </c>
       <c r="E39" t="n">
-        <v>79.33333333333333</v>
+        <v>139</v>
       </c>
       <c r="F39" t="n">
-        <v>1619.15</v>
+        <v>1899.516961766281</v>
       </c>
       <c r="G39" t="n">
-        <v>6862.426666666666</v>
+        <v>6285.616036365866</v>
       </c>
       <c r="H39" t="n">
-        <v>1.666666666666667</v>
+        <v>3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -10527,96 +10527,30 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12261</v>
+        <v>24770</v>
       </c>
       <c r="E40" t="n">
-        <v>79.33333333333333</v>
+        <v>82</v>
       </c>
       <c r="F40" t="n">
-        <v>1619.15</v>
+        <v>1111.223038233719</v>
       </c>
       <c r="G40" t="n">
-        <v>6862.426666666666</v>
+        <v>3677.103963634135</v>
       </c>
       <c r="H40" t="n">
-        <v>1.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>33556.5</v>
-      </c>
-      <c r="E41" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1505.37</v>
-      </c>
-      <c r="G41" t="n">
-        <v>4981.360000000001</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>33556.5</v>
-      </c>
-      <c r="E42" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1505.37</v>
-      </c>
-      <c r="G42" t="n">
-        <v>4981.360000000001</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2</v>
-      </c>
-      <c r="I42" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week20.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week20.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
